--- a/pyBACKUPS/config.xlsx
+++ b/pyBACKUPS/config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1abb604d7086dfb/Documents/GitHub/hrfc-welcome-pack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB9FF86C-123C-45BB-8C1C-F5D645F0EA5B}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5540CD87-F0E9-48EE-8DAB-5829EC4E31C7}"/>
   <bookViews>
-    <workbookView xWindow="22335" yWindow="2145" windowWidth="28155" windowHeight="13545" activeTab="3" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
+    <workbookView xWindow="4320" yWindow="4290" windowWidth="28155" windowHeight="15300" activeTab="1" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
   </bookViews>
   <sheets>
     <sheet name="pitch_anchors" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="229">
   <si>
     <t>pitch_key</t>
   </si>
@@ -566,9 +566,6 @@
     <t>Oaks RFC</t>
   </si>
   <si>
-    <t>R&amp;A</t>
-  </si>
-  <si>
     <t>RWB RFC</t>
   </si>
   <si>
@@ -714,6 +711,24 @@
   </si>
   <si>
     <t>text_fg</t>
+  </si>
+  <si>
+    <t>Walcats</t>
+  </si>
+  <si>
+    <t>WALCATS</t>
+  </si>
+  <si>
+    <t>Minety RFC &amp; Cricklade RFC</t>
+  </si>
+  <si>
+    <t>MRFC &amp; CRFC</t>
+  </si>
+  <si>
+    <t>MINETY &amp; CRICKLADE</t>
+  </si>
+  <si>
+    <t>RRFC &amp; ARFC</t>
   </si>
 </sst>
 </file>
@@ -2095,7 +2110,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5837B33A-C646-4048-BB46-7ABB988B4ED9}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" customWidth="1"/>
@@ -2152,7 +2167,7 @@
         <v>137</v>
       </c>
       <c r="B5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
@@ -2215,7 +2230,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B11" t="s">
         <v>74</v>
@@ -2394,7 +2409,7 @@
         <v>104</v>
       </c>
       <c r="B27" t="s">
-        <v>174</v>
+        <v>228</v>
       </c>
       <c r="C27" t="s">
         <v>105</v>
@@ -2405,7 +2420,7 @@
         <v>157</v>
       </c>
       <c r="B28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C28" t="s">
         <v>106</v>
@@ -2563,6 +2578,28 @@
       </c>
       <c r="C42" t="s">
         <v>172</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>223</v>
+      </c>
+      <c r="B43" t="s">
+        <v>223</v>
+      </c>
+      <c r="C43" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>225</v>
+      </c>
+      <c r="B44" t="s">
+        <v>226</v>
+      </c>
+      <c r="C44" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2583,27 +2620,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" t="s">
         <v>209</v>
       </c>
-      <c r="C1" t="s">
-        <v>210</v>
-      </c>
       <c r="D1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D2">
         <v>14</v>
@@ -2611,7 +2648,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D3">
         <v>13</v>
@@ -2619,7 +2656,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D4">
         <v>12</v>
@@ -2627,7 +2664,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D5">
         <v>11</v>
@@ -2635,7 +2672,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -2643,7 +2680,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -2651,7 +2688,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D8">
         <v>8</v>
@@ -2662,19 +2699,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F9">
         <v>50</v>
@@ -2682,19 +2719,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D10">
         <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F10">
         <v>50</v>
@@ -2702,19 +2739,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F11">
         <v>50</v>
@@ -2722,19 +2759,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F12">
         <v>60</v>
@@ -2742,19 +2779,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F13">
         <v>70</v>
@@ -2762,19 +2799,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F14">
         <v>40</v>
@@ -2782,19 +2819,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F15">
         <v>50</v>
@@ -2802,19 +2839,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F16">
         <v>50</v>
@@ -2822,19 +2859,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F17">
         <v>50</v>
@@ -2842,19 +2879,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D18">
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F18">
         <v>60</v>
@@ -2862,19 +2899,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D19">
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F19">
         <v>60</v>
@@ -2899,42 +2936,42 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" t="s">
         <v>177</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>178</v>
       </c>
-      <c r="C1" t="s">
-        <v>179</v>
-      </c>
       <c r="D1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G1" t="s">
         <v>222</v>
-      </c>
-      <c r="G1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F2" t="str">
         <f>D2</f>
@@ -2947,19 +2984,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" t="s">
         <v>183</v>
       </c>
-      <c r="C3" t="s">
-        <v>184</v>
-      </c>
       <c r="D3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F3" t="str">
         <f>D3</f>
